--- a/baseline/data_processing_elements-SHR.xlsx
+++ b/baseline/data_processing_elements-SHR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\twey working files\ProPASS\SHR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6C65A51-8F05-4AC5-B5A5-4C6DA6FE40AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BA6DA62-930E-41F7-9621-159DB4E96A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{183527E9-C397-49D1-929F-7CE96446A080}"/>
+    <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="15720" xr2:uid="{183527E9-C397-49D1-929F-7CE96446A080}"/>
   </bookViews>
   <sheets>
     <sheet name="Processing elements" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="496">
   <si>
     <t>compatible</t>
   </si>
@@ -363,9 +363,6 @@
     <t>input_labels</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>int_year;
 int_month</t>
   </si>
@@ -375,39 +372,9 @@
 </t>
   </si>
   <si>
-    <t>-9. Not applicable;
--2. Refusal;
--1. Don't know</t>
-  </si>
-  <si>
-    <t>MALE OR FEMALE</t>
-  </si>
-  <si>
-    <t>1. Male;
-2. Female;
--2. Refusal;
--1. Don't know</t>
-  </si>
-  <si>
     <t>Age of respondent at the time of interview</t>
   </si>
   <si>
-    <t>TOTAL HOURS WORKED PER WEEK</t>
-  </si>
-  <si>
-    <t>HOW TALL ARE YOU?</t>
-  </si>
-  <si>
-    <t>WEIGHT OF RESPONDENT</t>
-  </si>
-  <si>
-    <t>EVER SMOKED DAILY;
-SMOKE AT THE PRESENT TIME</t>
-  </si>
-  <si>
-    <t>AVERAGE AMOUNT OF CIGARETTES PER DAY</t>
-  </si>
-  <si>
     <t>Health in general question 2</t>
   </si>
   <si>
@@ -490,9 +457,6 @@
   </si>
   <si>
     <t>recode(1=2; 2=2; 3=2; 4=1; 5=3; 6=4; ELSE=NA)</t>
-  </si>
-  <si>
-    <t>HOW OFTEN A WEEK DO YOU CONSUME A SERVING OF FRUITS OR VEGETABLES</t>
   </si>
   <si>
     <t>1 = Every day;
@@ -507,23 +471,10 @@
 </t>
   </si>
   <si>
-    <t>case_when(
-  4 %in% PH006_DocCond ~ 1L;
-  !(4 %in% PH006_DocCond) &amp; !is.na(PH006_DocCond) ~ 2L;
-  ELSE ~ NA_integer_
-)</t>
-  </si>
-  <si>
     <t>Cancer ever</t>
   </si>
   <si>
-    <t>TROUBLE SLEEPING</t>
-  </si>
-  <si>
     <t>recode(1=1; 2=0; ELSE=NA)</t>
-  </si>
-  <si>
-    <t>SPORTS OR ACTIVITIES THAT ARE VIGOROUS ; ACTIVITIES REQUIRING A MODERATE LEVEL OF ENERGY</t>
   </si>
   <si>
     <t>adm_participant_id</t>
@@ -830,16 +781,6 @@
     <t>Current job situation</t>
   </si>
   <si>
-    <t>-2 = Refusal
--1 = Don't know
-1 = Retired 
-2 = Employed or self-employed 
-3 = Unemployed
-4 = Permanently sick or disabled 
-5 = Homemaker
-97 = Other</t>
-  </si>
-  <si>
     <t>dn042_</t>
   </si>
   <si>
@@ -901,20 +842,7 @@
     <t>br006_</t>
   </si>
   <si>
-    <t>br006_ * 7</t>
-  </si>
-  <si>
     <t>ph003_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2 = Refusal;
--1 = Don't know;
-1 = Excellent;
-2 = Very good;
-3 = Good;
-4 = Fair;
-5 = Poor;
-</t>
   </si>
   <si>
     <t>recode(1=4; 2=4; 3=3; 4=2; 5=1; -2=NA ; -1=NA ; ELSE=NA)</t>
@@ -1253,9 +1181,6 @@
   </si>
   <si>
     <t>ep018_</t>
-  </si>
-  <si>
-    <t>WHICH INDUSTRY ACTIVE</t>
   </si>
   <si>
     <t>1. Agriculture, hunting, forestry, fishing;
@@ -1276,24 +1201,6 @@
 -1. Don't know</t>
   </si>
   <si>
-    <t>case_when(
-ep018_ == 1 ~ "Agriculture, hunting, forestry, fishing";
-ep018_ == 2 ~ "Mining and quarrying";
-ep018_ == 3 ~ "Manufacturing";
-ep018_ == 4 ~ "Electricity, gas and water supply";
-ep018_ == 5 ~ "Construction";
-ep018_ == 6 ~ "Wholesale and retail trade; repair of motor vehicles, motorcycles and personal and household goods";
-ep018_ == 7 ~ "Hotels and restaurants";
-ep018_ == 8 ~ "Transport, storage and communication";
-ep018_ == 9 ~ "Financial intermediation";
-ep018_ == 10 ~ "Real estate, renting and business activities";
-ep018_ == 11 ~ "Public administration and defence; compulsory social security";
-ep018_ == 12 ~ "Education";
-ep018_ == 13 ~ "Health and social work";
-ep018_ == 14 ~ "Other community, social and personal service activities";
-ELSE ~ NA_character_)</t>
-  </si>
-  <si>
     <t>recode(-2=NA; -1=NA; 0=0; 1=0; 2=0; 3=1; 4=2; 5=3; 6=3; 95=NA; 97=NA; ELSE=NA)</t>
   </si>
   <si>
@@ -1304,14 +1211,6 @@
   </si>
   <si>
     <t>ifelse(ep013_ &gt; 0, ep013_, NA)</t>
-  </si>
-  <si>
-    <t>case_when(
-iv009_ %in% c(1, 2, 3) ~ 2L;
-iv009_ %in% c(4, 5) ~ 1L;
-iv009_ %in% c(NA, -1, -2) &amp; areabldgi %in% c(1, 2, 3) ~ 2L;
-iv009_ %in% c(NA, -1, -2) &amp; areabldgi %in% c(4, 5) ~ 1L;
-ELSE ~ NA_integer_)</t>
   </si>
   <si>
     <t>iv009_;
@@ -1352,22 +1251,12 @@
     <t>The study question asked if participants had trouble sleeping recently.</t>
   </si>
   <si>
-    <t>-2 Refusal
--1 Don't know
-1 Trouble with sleep or recent change in pattern
-5 No trouble sleeping</t>
-  </si>
-  <si>
     <t>br039_ ; 
 br040_</t>
   </si>
   <si>
     <t>At least one alcoholic beverage the last 7 days ; 
 Units of alcoholic beverage the last seven days</t>
-  </si>
-  <si>
-    <t>The study question asked if participants ever smoked cigarettes, cigars, cigarillos
-or a pipe daily for a period of at least one year. Participants who did not smoke daily for a year were considered as never smokers. Participants who smoked daily for a year but who are not smoking at the present time were considered as previous smokers.</t>
   </si>
   <si>
     <t>-2 Refusal
@@ -1384,16 +1273,7 @@
     <t xml:space="preserve">Study category "Married, living separated from spouse" is coded as DataSchema category "Married/In a partnership/Living together". </t>
   </si>
   <si>
-    <t>Information from different waves was combined</t>
-  </si>
-  <si>
     <t>Study categories "Excellent" and "Very good" were combined into DataSchema category "Very good/Excellent".</t>
-  </si>
-  <si>
-    <t>recode(0=0; 1=1; ELSE=NA)</t>
-  </si>
-  <si>
-    <t>High blood cholesterol: ever diagnosed/currently having</t>
   </si>
   <si>
     <t>1. Selected;
@@ -1402,20 +1282,6 @@
 -1. Don't know</t>
   </si>
   <si>
-    <t>ph006d19;
-ph006d20</t>
-  </si>
-  <si>
-    <t>Rheumatoid arthritis: ever diagnosed/currently having;
-Osteoarthritis/other rheumatism: ever diagnosed/currently having</t>
-  </si>
-  <si>
-    <t>case_when(
-ph006d19 == 1 ~ 1L; 
-ph006d20 == 1 ~ 1L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
     <t>ph011d1</t>
   </si>
   <si>
@@ -1437,37 +1303,16 @@
     <t>Wording specifies medication currently taken at least once a week.</t>
   </si>
   <si>
-    <t>Alzheimer's disease, dementia, senility: ever diagnosed/currently having</t>
-  </si>
-  <si>
-    <t>recode(1 = 1 ; 0 = 0 ; -2 = NA ; -1 = NA ; ELSE = NA)</t>
-  </si>
-  <si>
     <t>ph006d16_ever</t>
   </si>
   <si>
     <t>ph006d3_ever</t>
   </si>
   <si>
-    <t>Heart attack: ever diagnosed/currently having</t>
-  </si>
-  <si>
-    <t>ph006d1_ever</t>
-  </si>
-  <si>
     <t>The study question wording combines myocardial infarction with multiple other conditions: "A heart attack including myocardial infarction or coronary thrombosis or any other heart problem including congestive heart failure".</t>
   </si>
   <si>
-    <t>ph006d4_ever</t>
-  </si>
-  <si>
-    <t>Stroke: ever diagnosed/currently having</t>
-  </si>
-  <si>
     <t>ph006d2_ever</t>
-  </si>
-  <si>
-    <t>High blood pressure or hypertension: ever diagnosed/currently having</t>
   </si>
   <si>
     <t>ph006d2_ever ; 
@@ -1478,18 +1323,7 @@
 Drugs for: high blood pressure</t>
   </si>
   <si>
-    <t>case_when(
-  ph006d2_ever == 1 | ph011d2 == 1 ~ 1L ; 
-  ph006d2_ever == 0 &amp; ph011d2 == 0 ~ 0L ;   
-  ph006d2_ever == 0 | ph011d2 == 0 ~ 2L ;   
-  ELSE ~ NA_integer_
-)</t>
-  </si>
-  <si>
     <t>The study question wording does not distinguish between diabetes and high blood sugar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heart attack: ever diagnosed/currently having </t>
   </si>
   <si>
     <t>Study question wording included "A heart attack including myocardial infarction or coronary thrombosis or any other heart problem including congestive heart failure". The DataSchema category "No" could not be coded.</t>
@@ -1654,211 +1488,390 @@
     <t>Study only asked about cancer in endometrium. Endoetrium cancer is coded as yes, but cannot code "no" in DataSchema variable.</t>
   </si>
   <si>
+    <t>Alcohol quantity consumption based on last 7 days. 
+Conversion of 10g/unit used based on reference article: doi.org/10.1080/13607863.2022.2076208.</t>
+  </si>
+  <si>
+    <t>br029_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dn014_latest  </t>
+  </si>
+  <si>
+    <t>updates_per_cohort_comment</t>
+  </si>
+  <si>
+    <t>Updated variable name.</t>
+  </si>
+  <si>
+    <t>ph013_latest</t>
+  </si>
+  <si>
+    <t>ifelse(ph013_latest &gt; 0, ph013_latest, NA)</t>
+  </si>
+  <si>
+    <t>ifelse(ph013_latest &gt; 0, 1, NA)</t>
+  </si>
+  <si>
+    <t>Exact day of completion date was not available. All dates were set on the 15th of the month and year specified.</t>
+  </si>
+  <si>
+    <t>Hours worked per week available, but definition of full- and part-time will vary across countries.</t>
+  </si>
+  <si>
+    <t>lab_hba1c</t>
+  </si>
+  <si>
+    <t>Changed to presumed no to account for select all that apply question structure and potential missing waves of data.</t>
+  </si>
+  <si>
+    <t>Updated input variables and algorithm. 
+Changed to presumed no to account for select all that apply question structure and potential missing waves of data.
+One participant refused to answer at one wave: Coded as NA.</t>
+  </si>
+  <si>
+    <t>CVD</t>
+  </si>
+  <si>
+    <t>case_when(
+  ph006d2_ever == 1 | ph011d2 == 1 ~ 1L ; 
+  ph006d2_ever == 0 | ph011d2 == 0 ~ 2L ;   
+  ELSE ~ NA_integer_
+)</t>
+  </si>
+  <si>
+    <t>recode(1 = 1 ; 0 = 2 ; ELSE = NA)</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
     <t>case_when(
   ph008d19_ever == 1 | ph080d19_ever == 1 ~ 1L ;
-  ph008d19_ever == 0 &amp; ph080d19_ever == 0 ~ 0L ;
+  ph008d19_ever == 0 &amp; ph080d19_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d7_ever == 1 | ph080d7_ever == 1 ~ 1L ;
-  ph008d7_ever == 0 &amp; ph080d7_ever == 0 ~ 0L ;
+  ph008d7_ever == 0 &amp; ph080d7_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d16_ever == 1 | ph080d16_ever == 1 ~ 1L ;
-  ph008d16_ever == 0 &amp; ph080d16_ever == 0 ~ 0L ;
+  ph008d16_ever == 0 &amp; ph080d16_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d18_ever == 1 | ph080d18_ever == 1 ~ 1L ;
-  ph008d18_ever == 0 &amp; ph080d18_ever == 0 ~ 0L ;
+  ph008d18_ever == 0 &amp; ph080d18_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d12_ever == 1 | ph080d12_ever == 1 ~ 1L ;
-  ph008d12_ever == 0 &amp; ph080d12_ever == 0 ~ 0L ;
+  ph008d12_ever == 0 &amp; ph080d12_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d3_ever == 1 | ph008d4_ever == 1 | ph080d3_ever == 1 | ph080d4_ever == 1 ~ 1L ;
-  ph008d3_ever == 0 &amp; ph008d4_ever == 0 &amp; ph080d3_ever == 0 | ph080d4_ever ~ 0L ;
+  ph008d3_ever == 0 &amp; ph008d4_ever == 0 &amp; ph080d3_ever == 0 | ph080d4_ever ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d22_ever == 1 | ph080d22_ever == 1 ~ 1L ;
-  ph008d22_ever == 0 &amp; ph080d22_ever == 0 ~ 0L ;
+  ph008d22_ever == 0 &amp; ph080d22_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d6_ever == 1 | ph080d6_ever == 1 ~ 1L ;
-  ph008d6_ever == 0 &amp; ph080d6_ever == 0 ~ 0L ;
+  ph008d6_ever == 0 &amp; ph080d6_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d21_ever == 1 | ph080d21_ever == 1 ~ 1L ;
-  ph008d21_ever == 0 &amp; ph080d21_ever == 0 ~ 0L ;
+  ph008d21_ever == 0 &amp; ph080d21_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d13_ever == 1 | ph080d13_ever == 1 ~ 1L ;
-  ph008d13_ever == 0 &amp; ph080d13_ever == 0 ~ 0L ;
+  ph008d13_ever == 0 &amp; ph080d13_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d20_ever == 1 | ph080d20_ever == 1 ~ 1L ;
-  ph008d20_ever == 0 &amp; ph080d20_ever == 0 ~ 0L ;
+  ph008d20_ever == 0 &amp; ph080d20_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d9_ever == 1 | ph080d9_ever == 1 ~ 1L ;
-  ph008d9_ever == 0 &amp; ph080d9_ever == 0 ~ 0L ;
+  ph008d9_ever == 0 &amp; ph080d9_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d14_ever == 1 | ph080d14_ever == 1 ~ 1L ;
-  ph008d14_ever == 0 &amp; ph080d14_ever == 0 ~ 0L ;
+  ph008d14_ever == 0 &amp; ph080d14_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d17_ever == 1 | ph080d17_ever == 1 ~ 1L ;
-  ph008d17_ever == 0 &amp; ph080d17_ever == 0 ~ 0L ;
+  ph008d17_ever == 0 &amp; ph080d17_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d1_ever == 1 | ph080d1_ever == 1 ~ 1L ;
-  ph008d1_ever == 0 &amp; ph080d1_ever == 0 ~ 0L ;
+  ph008d1_ever == 0 &amp; ph080d1_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d10_ever == 1 | ph080d10_ever == 1 ~ 1L ;
-  ph008d10_ever == 0 &amp; ph080d10_ever == 0 ~ 0L ;
+  ph008d10_ever == 0 &amp; ph080d10_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d15_ever == 1 | ph080d15_ever == 1 ~ 1L ;
-  ph008d15_ever == 0 &amp; ph080d15_ever == 0 ~ 0L ;
+  ph008d15_ever == 0 &amp; ph080d15_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d11_ever == 1 | ph080d11_ever == 1 ~ 1L ;
-  ph008d11_ever == 0 &amp; ph080d11_ever == 0 ~ 0L ;
+  ph008d11_ever == 0 &amp; ph080d11_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
     <t>case_when(
   ph008d5_ever == 1 | ph080d5_ever == 1 ~ 1L ;
-  ph008d5_ever == 0 &amp; ph080d5_ever == 0 ~ 0L ;
+  ph008d5_ever == 0 &amp; ph080d5_ever == 0 ~ 2L ;
   ELSE ~ NA_integer_
 )</t>
   </si>
   <si>
-    <t>Alcohol quantity consumption based on last 7 days. 
-Conversion of 10g/unit used based on reference article: doi.org/10.1080/13607863.2022.2076208.</t>
-  </si>
-  <si>
-    <t>br029_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dn014_latest  </t>
-  </si>
-  <si>
-    <t>updates_per_cohort_comment</t>
-  </si>
-  <si>
-    <t>Updated variable name.</t>
-  </si>
-  <si>
-    <t>ph013_latest</t>
-  </si>
-  <si>
-    <t>ifelse(ph013_latest &gt; 0, ph013_latest, NA)</t>
-  </si>
-  <si>
-    <t>ifelse(ph013_latest &gt; 0, 1, NA)</t>
-  </si>
-  <si>
-    <t>Only available since wave 2.</t>
-  </si>
-  <si>
-    <t>Collected information included rheumatoid arthritis, and osteoarthritis or other rheumatism. The DataSchema category "No" could not be coded.
-Only collected since wave 5.</t>
-  </si>
-  <si>
-    <t>Updated input variables and algorithm.</t>
+    <t>Variable derived by study. Only available since wave 2.</t>
+  </si>
+  <si>
+    <t>Person identifier (fix across modules and waves)</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>Numeric (int) ; 
+Numeric (byte)</t>
+  </si>
+  <si>
+    <t>Male or female</t>
+  </si>
+  <si>
+    <t>1. Male;
+2. Female</t>
+  </si>
+  <si>
+    <t>1 = Retired 
+2 = Employed or self-employed 
+3 = Unemployed
+4 = Permanently sick or disabled 
+5 = Homemaker
+97 = Other</t>
+  </si>
+  <si>
+    <t>Total hours usually working per week</t>
+  </si>
+  <si>
+    <t>Numeric (int) ; Range: [-2,80]</t>
+  </si>
+  <si>
+    <t>Kind of industry working in</t>
+  </si>
+  <si>
+    <t>case_when(
+iv009_ %in% c(1, 2, 3) ~ 2L;
+iv009_ %in% c(4, 5) ~ 1L;
+areabldgi %in% c(1, 2, 3) ~ 2L;
+areabldgi %in% c(4, 5) ~ 1L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>Weight of respondent</t>
+  </si>
+  <si>
+    <t>Height: Latest information (combined information from different waves)</t>
+  </si>
+  <si>
+    <t>How often serving of fruits or vegetables</t>
+  </si>
+  <si>
+    <t>Ever smoked daily;
+Smoke at the present time</t>
+  </si>
+  <si>
+    <t>Average amount of cigarettes per day</t>
+  </si>
+  <si>
+    <t>ifelse(br006_ &gt; 0, br006_, NA)</t>
+  </si>
+  <si>
+    <t>Study variable combines fruits and vegetables.</t>
+  </si>
+  <si>
+    <t>The study question asked if participants ever smoked cigarettes, cigars, cigarillos or a pipe daily for a period of at least one year. Participants who did not smoke daily for a year were considered as never smokers. Participants who smoked daily for a year but who are not smoking at the present time were considered as previous smokers.</t>
+  </si>
+  <si>
+    <t>Trouble sleeping</t>
+  </si>
+  <si>
+    <t>-2 Refusal
+-1 Don't know
+1 Trouble with sleep or recent change in pattern
+2 No trouble sleeping</t>
+  </si>
+  <si>
+    <t>Sports or activities that are vigorous ;
+Activities requiring a moderate level of energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2 = Refusal;
+-1 = Don't know;
+1 = Excellent;
+2 = Very good;
+3 = Good;
+4 = Fair;
+5 = Poor
+</t>
+  </si>
+  <si>
+    <t>1. Selected;
+0. Not selected;
+-2. Refusal;
+-1. Don't know ; 
+1 Yes , 5 No</t>
+  </si>
+  <si>
+    <t>The study question wording combines stroke with multiple other cerebral vascular disease.</t>
+  </si>
+  <si>
+    <t>Ever mentioned (wave 1-8): High blood pressure or hypertension</t>
+  </si>
+  <si>
+    <t>Ever mentioned (wave 1-8): High blood cholesterol</t>
+  </si>
+  <si>
+    <t>Ever mentioned (wave 2-8): Alzheimer's disease, dementia, organic brain syndrome</t>
+  </si>
+  <si>
+    <t>ph006d8_ever ; 
+ph006d19_ever ; 
+ph006d20_ever</t>
+  </si>
+  <si>
+    <t>Ever mentioned (wave 1-4): Arthritis, including osteoarthritis, or rheumatism ; 
+Ever mentioned (wave 5-8): Rheumatoid Arthritis ; 
+Ever mentioned (wave 5-8): Osteoarthritis, or other rheumatism</t>
   </si>
   <si>
     <t>ph006d1_ever ; 
-ph006d4_ever ; 
-ph006d2_ever</t>
-  </si>
-  <si>
-    <t>Heart attack: ever diagnosed/currently having ; 
-Stroke: ever diagnosed/currently having ; 
-High blood pressure or hypertension: ever diagnosed/currently having</t>
-  </si>
-  <si>
-    <t>Collected information included Heart attack, myocardial infarction, coronary thrombosis, any other heart problem including congestive heart failure, hypertension, stroke and cerebrovascular disease. 
-Only presence of condition, not absence) could be assigned, so only 1 or NA values present in harmonized variable.
-Information from different waves was combined.</t>
-  </si>
-  <si>
-    <t>Cancer or malignant tumour, including leukaemia or lymphoma, but excluding minor skin cancers</t>
-  </si>
-  <si>
-    <t>ph006d10_ever</t>
-  </si>
-  <si>
-    <t>Updated input variables and algorithm. But need to verify that this is available.</t>
-  </si>
-  <si>
-    <t>Exact day of completion date was not available. All dates were set on the 15th of the month and year specified.</t>
-  </si>
-  <si>
-    <t>Hours worked per week available, but definition of full- and part-time will vary across countries.</t>
-  </si>
-  <si>
-    <t>lab_hba1c</t>
+ph067_1_ever ; 
+ph072_1_ever</t>
+  </si>
+  <si>
+    <t>Ever mentioned (wave 1-8): A heart attack including myocardial infarction or cor ; 
+wave 2: Had a heart attack since last interview ; 
+Ever mentioned (wave 4-8): Had a heart attack since last interview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ph006d4_ever ; 
+ph067_2_ever ; 
+ph072_2_ever </t>
+  </si>
+  <si>
+    <t>Ever mentioned (wave 1-8): A stroke or cerebral vascular disease ; 
+wave 2: Had a stroke/been diagnosed with cerebral vascular disease since last in ; 
+Ever mentioned (wave 4-8): Had a stroke/diagnosed with cerebral vascular disease</t>
+  </si>
+  <si>
+    <t>Ever mentioned: Cardiovascular disease</t>
+  </si>
+  <si>
+    <t>1. Yes;
+0. No;
+-2. Refusal;
+-1. Don't know</t>
+  </si>
+  <si>
+    <t>Variable derived by study across all waves of collect. Individual conditions were asked about in "select all that apply" format and could be missing at individual waves of collect.</t>
+  </si>
+  <si>
+    <t>Ever mentioned: Cancer</t>
+  </si>
+  <si>
+    <t>recode(1 = 1 ; 0 = 2 ; -2 = NA ; -1 = NA ; ELSE = NA)</t>
   </si>
   <si>
     <t>case_when(
-  ph006d1_ever ==1 | ph006d4_ever == 1 | ph006d2_ever == 1 ~ 1L ; 
+  ph006d1_ever == 1 | ph067_1_ever == 1 | ph072_1_ever == 1 ~ 1L ; 
   ELSE ~ NA_integer_
 )</t>
+  </si>
+  <si>
+    <t>Collected information included arthritis, rheumatoid arthritis, and osteoarthritis or other rheumatism. The DataSchema category "No" could not be coded.</t>
+  </si>
+  <si>
+    <t>case_when(
+  ph006d8_ever == 1 | ph006d19_ever == 1 | ph006d20_ever == 1 ~ 1L; 
+  ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>Changed to presumed no to account for select all that apply question structure.</t>
+  </si>
+  <si>
+    <t>case_when(_x000D_
+ep018_ == 1 ~ "Agriculture, hunting, forestry, fishing";_x000D_
+ep018_ == 2 ~ "Mining and quarrying";_x000D_
+ep018_ == 3 ~ "Manufacturing";_x000D_
+ep018_ == 4 ~ "Electricity, gas and water supply";_x000D_
+ep018_ == 5 ~ "Construction";_x000D_
+ep018_ == 6 ~ "Wholesale and retail trade; repair of motor vehicles, motorcycles and personal and household goods";_x000D_
+ep018_ == 7 ~ "Hotels and restaurants";_x000D_
+ep018_ == 8 ~ "Transport, storage and communication";_x000D_
+ep018_ == 9 ~ "Financial intermediation";_x000D_
+ep018_ == 10 ~ "Real estate, renting and business activities";_x000D_
+ep018_ == 11 ~ "Public administration and defence; compulsory social security";_x000D_
+ep018_ == 12 ~ "Education";_x000D_
+ep018_ == 13 ~ "Health and social work";_x000D_
+ep018_ == 14 ~ "Other community, social and personal service activities";_x000D_
+ELSE ~ NA_character_)</t>
   </si>
 </sst>
 </file>
@@ -1913,7 +1926,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1944,6 +1957,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1959,7 +1978,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2002,6 +2021,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2349,7 +2374,7 @@
         <v>9</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>79</v>
@@ -2388,33 +2413,33 @@
         <v>18</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>81</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>88</v>
+        <v>453</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1" t="s">
@@ -2438,19 +2463,19 @@
         <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>255</v>
+        <v>239</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1" t="s">
@@ -2460,10 +2485,10 @@
         <v>4</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -2474,14 +2499,14 @@
         <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>20</v>
@@ -2489,7 +2514,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="1" t="s">
@@ -2499,10 +2524,10 @@
         <v>4</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="P4" s="8"/>
     </row>
@@ -2514,19 +2539,19 @@
         <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1" t="s">
@@ -2536,10 +2561,10 @@
         <v>4</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -2550,28 +2575,28 @@
         <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>91</v>
+        <v>455</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>488</v>
+        <v>424</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>1</v>
@@ -2586,7 +2611,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -2594,7 +2619,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>55</v>
@@ -2603,19 +2628,19 @@
         <v>53</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>92</v>
+        <v>456</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>93</v>
+        <v>457</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
@@ -2639,22 +2664,25 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>454</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
@@ -2667,7 +2695,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="174" x14ac:dyDescent="0.35">
@@ -2675,31 +2703,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
@@ -2712,7 +2740,7 @@
         <v>2</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="174" x14ac:dyDescent="0.35">
@@ -2720,10 +2748,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>56</v>
@@ -2732,19 +2760,19 @@
         <v>53</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
@@ -2757,7 +2785,7 @@
         <v>2</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -2768,7 +2796,7 @@
         <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>56</v>
@@ -2777,13 +2805,13 @@
         <v>53</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
@@ -2807,7 +2835,7 @@
         <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>56</v>
@@ -2816,13 +2844,13 @@
         <v>53</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
@@ -2846,7 +2874,7 @@
         <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>56</v>
@@ -2855,13 +2883,13 @@
         <v>53</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
@@ -2885,7 +2913,7 @@
         <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>56</v>
@@ -2894,13 +2922,13 @@
         <v>53</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
@@ -2924,7 +2952,7 @@
         <v>31</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>56</v>
@@ -2933,13 +2961,13 @@
         <v>53</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
@@ -2963,7 +2991,7 @@
         <v>32</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>56</v>
@@ -2972,13 +3000,13 @@
         <v>53</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
@@ -3002,7 +3030,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>56</v>
@@ -3011,13 +3039,13 @@
         <v>53</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
@@ -3041,7 +3069,7 @@
         <v>34</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>56</v>
@@ -3050,13 +3078,13 @@
         <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1" t="s">
@@ -3080,7 +3108,7 @@
         <v>35</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>56</v>
@@ -3089,13 +3117,13 @@
         <v>53</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="2" t="s">
@@ -3111,7 +3139,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="116" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -3119,7 +3147,7 @@
         <v>36</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>57</v>
@@ -3128,19 +3156,19 @@
         <v>53</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>232</v>
+        <v>458</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
@@ -3153,7 +3181,7 @@
         <v>2</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -3164,7 +3192,7 @@
         <v>37</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>58</v>
@@ -3173,19 +3201,22 @@
         <v>53</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>95</v>
+        <v>459</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>460</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>489</v>
+        <v>425</v>
       </c>
       <c r="L21" s="1" t="s">
         <v>6</v>
@@ -3208,22 +3239,25 @@
         <v>38</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>95</v>
+        <v>459</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>460</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
@@ -3236,7 +3270,7 @@
         <v>3</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="290" x14ac:dyDescent="0.35">
@@ -3247,26 +3281,26 @@
         <v>39</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>356</v>
+        <v>461</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1" t="s">
@@ -3275,11 +3309,11 @@
       <c r="M23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="N23" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="O23" s="1" t="s">
-        <v>358</v>
+      <c r="O23" s="17" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="130.5" x14ac:dyDescent="0.35">
@@ -3290,7 +3324,7 @@
         <v>40</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>59</v>
@@ -3299,19 +3333,19 @@
         <v>53</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1" t="s">
@@ -3324,7 +3358,7 @@
         <v>2</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="116" x14ac:dyDescent="0.35">
@@ -3335,7 +3369,7 @@
         <v>41</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>60</v>
@@ -3344,22 +3378,22 @@
         <v>53</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>473</v>
+        <v>418</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>1</v>
@@ -3371,10 +3405,10 @@
         <v>2</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>475</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
@@ -3385,7 +3419,7 @@
         <v>42</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>61</v>
@@ -3394,19 +3428,19 @@
         <v>53</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>84</v>
@@ -3421,7 +3455,7 @@
         <v>7</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>363</v>
+        <v>462</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -3429,28 +3463,28 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>476</v>
+        <v>421</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>96</v>
+        <v>464</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1" t="s">
@@ -3463,10 +3497,10 @@
         <v>3</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>477</v>
+        <v>422</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>475</v>
+        <v>420</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -3474,10 +3508,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>62</v>
@@ -3486,16 +3520,19 @@
         <v>53</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>476</v>
+        <v>421</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>96</v>
+        <v>464</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="1" t="s">
@@ -3508,10 +3545,10 @@
         <v>3</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>478</v>
+        <v>423</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>475</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -3522,25 +3559,25 @@
         <v>5</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>97</v>
+        <v>463</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="1" t="s">
@@ -3553,7 +3590,7 @@
         <v>3</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -3561,10 +3598,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>62</v>
@@ -3573,16 +3610,19 @@
         <v>53</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>97</v>
+        <v>463</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="1" t="s">
@@ -3595,7 +3635,7 @@
         <v>3</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -3603,28 +3643,28 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="1" t="s">
@@ -3637,7 +3677,7 @@
         <v>3</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
@@ -3645,22 +3685,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="1" t="s">
@@ -3681,10 +3721,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>62</v>
@@ -3693,13 +3733,13 @@
         <v>53</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="1" t="s">
@@ -3720,22 +3760,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="1" t="s">
@@ -3756,22 +3796,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1" t="s">
@@ -3792,22 +3832,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1" t="s">
@@ -3828,22 +3868,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1" t="s">
@@ -3864,22 +3904,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="1" t="s">
@@ -3900,22 +3940,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1" t="s">
@@ -3939,7 +3979,7 @@
         <v>43</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>63</v>
@@ -3948,13 +3988,13 @@
         <v>53</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="1" t="s">
@@ -3975,22 +4015,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="1" t="s">
@@ -4011,22 +4051,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>490</v>
+        <v>426</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42" s="1" t="s">
@@ -4047,22 +4087,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="1" t="s">
@@ -4086,19 +4126,19 @@
         <v>44</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="1" t="s">
@@ -4122,19 +4162,19 @@
         <v>45</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1" t="s">
@@ -4158,19 +4198,19 @@
         <v>46</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1" t="s">
@@ -4191,22 +4231,22 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1" t="s">
@@ -4227,22 +4267,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1" t="s">
@@ -4263,22 +4303,22 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1" t="s">
@@ -4299,33 +4339,35 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>472</v>
+        <v>417</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>128</v>
+        <v>465</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="K50" s="1"/>
+        <v>336</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>469</v>
+      </c>
       <c r="L50" s="1" t="s">
         <v>6</v>
       </c>
@@ -4344,22 +4386,22 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1" t="s">
@@ -4380,10 +4422,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>64</v>
@@ -4392,21 +4434,23 @@
         <v>53</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>472</v>
+        <v>417</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>128</v>
+        <v>465</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="K52" s="1"/>
+        <v>336</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>469</v>
+      </c>
       <c r="L52" s="1" t="s">
         <v>6</v>
       </c>
@@ -4425,22 +4469,22 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1" t="s">
@@ -4461,31 +4505,31 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>471</v>
+        <v>416</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>1</v>
@@ -4497,7 +4541,7 @@
         <v>7</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="58" x14ac:dyDescent="0.35">
@@ -4505,10 +4549,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>65</v>
@@ -4517,13 +4561,13 @@
         <v>53</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1" t="s">
@@ -4544,10 +4588,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>66</v>
@@ -4556,22 +4600,22 @@
         <v>53</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>98</v>
+        <v>466</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>377</v>
+        <v>470</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>1</v>
@@ -4583,7 +4627,7 @@
         <v>7</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="29" x14ac:dyDescent="0.35">
@@ -4591,10 +4635,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>67</v>
@@ -4603,13 +4647,13 @@
         <v>53</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="1" t="s">
@@ -4630,10 +4674,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>54</v>
@@ -4642,16 +4686,16 @@
         <v>53</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>99</v>
+        <v>467</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1" t="s">
@@ -4664,7 +4708,7 @@
         <v>3</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>244</v>
+        <v>468</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="29" x14ac:dyDescent="0.35">
@@ -4672,22 +4716,22 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1" t="s">
@@ -4708,10 +4752,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>72</v>
@@ -4720,13 +4764,13 @@
         <v>53</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1" t="s">
@@ -4742,15 +4786,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" ht="81.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>73</v>
@@ -4759,22 +4803,22 @@
         <v>53</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>374</v>
+        <v>471</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>472</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>1</v>
@@ -4786,7 +4830,7 @@
         <v>2</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
@@ -4794,10 +4838,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>74</v>
@@ -4806,13 +4850,13 @@
         <v>53</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1" t="s">
@@ -4833,10 +4877,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>74</v>
@@ -4845,13 +4889,13 @@
         <v>53</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1" t="s">
@@ -4872,10 +4916,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>74</v>
@@ -4884,13 +4928,13 @@
         <v>53</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1" t="s">
@@ -4911,10 +4955,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>75</v>
@@ -4923,14 +4967,14 @@
         <v>53</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H65" s="2"/>
       <c r="J65" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1" t="s">
@@ -4951,10 +4995,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>74</v>
@@ -4963,13 +5007,13 @@
         <v>53</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1" t="s">
@@ -4990,10 +5034,10 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>74</v>
@@ -5002,13 +5046,13 @@
         <v>53</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1" t="s">
@@ -5029,22 +5073,22 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K68" s="1"/>
       <c r="L68" s="1" t="s">
@@ -5065,10 +5109,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>76</v>
@@ -5077,13 +5121,13 @@
         <v>53</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1" t="s">
@@ -5104,10 +5148,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>77</v>
@@ -5116,14 +5160,14 @@
         <v>53</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H70" s="2"/>
       <c r="J70" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1" t="s">
@@ -5144,10 +5188,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>78</v>
@@ -5156,13 +5200,13 @@
         <v>53</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1" t="s">
@@ -5183,10 +5227,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>56</v>
@@ -5195,22 +5239,22 @@
         <v>53</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>135</v>
+        <v>473</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>6</v>
@@ -5230,10 +5274,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>56</v>
@@ -5242,13 +5286,13 @@
         <v>53</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1" t="s">
@@ -5269,10 +5313,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>56</v>
@@ -5281,19 +5325,19 @@
         <v>53</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>135</v>
+        <v>473</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K74" s="1"/>
       <c r="L74" s="1" t="s">
@@ -5306,7 +5350,7 @@
         <v>7</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>251</v>
+        <v>235</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -5314,22 +5358,22 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="1" t="s">
@@ -5350,22 +5394,22 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="1" t="s">
@@ -5386,10 +5430,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>68</v>
@@ -5398,22 +5442,22 @@
         <v>53</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>246</v>
+        <v>474</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>1</v>
@@ -5425,18 +5469,18 @@
         <v>2</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" ht="116" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>69</v>
@@ -5445,22 +5489,22 @@
         <v>53</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="H78" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="I78" s="7" t="s">
-        <v>385</v>
+        <v>337</v>
+      </c>
+      <c r="G78" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="H78" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="I78" s="15" t="s">
+        <v>487</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K78" s="7" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>1</v>
@@ -5469,24 +5513,24 @@
         <v>0</v>
       </c>
       <c r="N78" s="7" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O78" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="P78" s="1" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
+        <v>431</v>
+      </c>
+      <c r="P78" s="7" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>69</v>
@@ -5495,22 +5539,22 @@
         <v>53</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>401</v>
+        <v>337</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>482</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>385</v>
+        <v>475</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>412</v>
+        <v>376</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>1</v>
@@ -5518,22 +5562,22 @@
       <c r="M79" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N79" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O79" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="N79" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="O79" s="7" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>69</v>
@@ -5542,22 +5586,22 @@
         <v>53</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>401</v>
+        <v>337</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>482</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>400</v>
+        <v>483</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>385</v>
+        <v>475</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>6</v>
@@ -5577,10 +5621,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>69</v>
@@ -5589,13 +5633,13 @@
         <v>53</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="1" t="s">
@@ -5611,15 +5655,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>69</v>
@@ -5628,22 +5672,22 @@
         <v>53</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>403</v>
+        <v>337</v>
+      </c>
+      <c r="G82" s="16" t="s">
+        <v>484</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>404</v>
+        <v>485</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>385</v>
+        <v>475</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>402</v>
+        <v>476</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>6</v>
@@ -5655,7 +5699,7 @@
         <v>6</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>131</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -5663,10 +5707,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>69</v>
@@ -5675,13 +5719,13 @@
         <v>53</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K83" s="1"/>
       <c r="L83" s="1" t="s">
@@ -5702,10 +5746,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>69</v>
@@ -5714,13 +5758,13 @@
         <v>53</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="1" t="s">
@@ -5741,10 +5785,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>69</v>
@@ -5753,19 +5797,19 @@
         <v>53</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>406</v>
+        <v>477</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K85" s="1"/>
       <c r="L85" s="1" t="s">
@@ -5777,19 +5821,22 @@
       <c r="N85" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O85" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="87" x14ac:dyDescent="0.35">
+      <c r="O85" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="P85" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>69</v>
@@ -5798,19 +5845,19 @@
         <v>53</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="1" t="s">
@@ -5822,19 +5869,22 @@
       <c r="N86" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O86" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="O86" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="P86" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>69</v>
@@ -5843,22 +5893,22 @@
         <v>53</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>386</v>
+        <v>337</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>480</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>387</v>
+        <v>481</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>480</v>
+        <v>336</v>
+      </c>
+      <c r="K87" s="7" t="s">
+        <v>492</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>1</v>
@@ -5870,7 +5920,7 @@
         <v>7</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>388</v>
+        <v>493</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
@@ -5878,10 +5928,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>69</v>
@@ -5890,16 +5940,16 @@
         <v>53</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>6</v>
@@ -5922,7 +5972,7 @@
         <v>47</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>70</v>
@@ -5931,13 +5981,13 @@
         <v>53</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K89" s="1"/>
       <c r="L89" s="1" t="s">
@@ -5958,10 +6008,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>69</v>
@@ -5970,37 +6020,37 @@
         <v>53</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="I90" s="7" t="s">
-        <v>385</v>
+        <v>337</v>
+      </c>
+      <c r="G90" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="H90" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="I90" s="15" t="s">
+        <v>487</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>381</v>
+        <v>336</v>
+      </c>
+      <c r="K90" s="7" t="s">
+        <v>488</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M90" s="1" t="s">
+      <c r="M90" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="N90" s="1" t="s">
+      <c r="N90" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="O90" s="1" t="s">
-        <v>383</v>
+      <c r="O90" s="7" t="s">
+        <v>431</v>
       </c>
       <c r="P90" s="7" t="s">
-        <v>487</v>
+        <v>427</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6008,10 +6058,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>69</v>
@@ -6020,19 +6070,19 @@
         <v>53</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G91" s="15" t="s">
-        <v>442</v>
+        <v>337</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>441</v>
+        <v>405</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K91" s="1"/>
       <c r="L91" s="1" t="s">
@@ -6044,8 +6094,11 @@
       <c r="N91" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O91" s="1" t="s">
-        <v>452</v>
+      <c r="O91" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="P91" s="7" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6053,10 +6106,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>69</v>
@@ -6065,19 +6118,19 @@
         <v>53</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G92" s="15" t="s">
-        <v>422</v>
+        <v>337</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>421</v>
+        <v>385</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1" t="s">
@@ -6089,8 +6142,11 @@
       <c r="N92" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O92" s="1" t="s">
-        <v>453</v>
+      <c r="O92" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="P92" s="7" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="93" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6098,10 +6154,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>69</v>
@@ -6110,19 +6166,19 @@
         <v>53</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G93" s="15" t="s">
-        <v>437</v>
+        <v>337</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>438</v>
+        <v>402</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K93" s="1"/>
       <c r="L93" s="1" t="s">
@@ -6134,8 +6190,11 @@
       <c r="N93" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O93" s="1" t="s">
-        <v>454</v>
+      <c r="O93" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="P93" s="7" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="94" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6143,10 +6202,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>69</v>
@@ -6155,19 +6214,19 @@
         <v>53</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G94" s="15" t="s">
-        <v>440</v>
+        <v>337</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="1" t="s">
@@ -6179,8 +6238,11 @@
       <c r="N94" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O94" s="1" t="s">
-        <v>455</v>
+      <c r="O94" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="P94" s="7" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
@@ -6188,10 +6250,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>69</v>
@@ -6200,19 +6262,19 @@
         <v>53</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G95" s="15" t="s">
-        <v>430</v>
+        <v>337</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>429</v>
+        <v>393</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K95" s="1"/>
       <c r="L95" s="1" t="s">
@@ -6224,8 +6286,11 @@
       <c r="N95" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O95" s="1" t="s">
-        <v>456</v>
+      <c r="O95" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="P95" s="7" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
@@ -6233,10 +6298,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>69</v>
@@ -6245,19 +6310,19 @@
         <v>53</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G96" s="15" t="s">
-        <v>415</v>
+        <v>337</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>379</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>416</v>
+        <v>380</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K96" s="1"/>
       <c r="L96" s="1" t="s">
@@ -6269,19 +6334,22 @@
       <c r="N96" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O96" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O96" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="P96" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>69</v>
@@ -6290,19 +6358,19 @@
         <v>53</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G97" s="15" t="s">
-        <v>448</v>
+        <v>337</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>412</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>447</v>
+        <v>411</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K97" s="1"/>
       <c r="L97" s="1" t="s">
@@ -6314,19 +6382,22 @@
       <c r="N97" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O97" s="1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O97" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="P97" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>69</v>
@@ -6335,19 +6406,19 @@
         <v>53</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G98" s="15" t="s">
-        <v>419</v>
+        <v>337</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>383</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>420</v>
+        <v>384</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K98" s="1"/>
       <c r="L98" s="1" t="s">
@@ -6359,19 +6430,22 @@
       <c r="N98" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O98" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O98" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="P98" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>69</v>
@@ -6380,19 +6454,19 @@
         <v>53</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G99" s="15" t="s">
-        <v>446</v>
+        <v>337</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>445</v>
+        <v>409</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K99" s="1"/>
       <c r="L99" s="1" t="s">
@@ -6404,19 +6478,22 @@
       <c r="N99" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O99" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O99" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="P99" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>69</v>
@@ -6425,19 +6502,19 @@
         <v>53</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G100" s="15" t="s">
-        <v>432</v>
+        <v>337</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K100" s="1"/>
       <c r="L100" s="1" t="s">
@@ -6449,19 +6526,22 @@
       <c r="N100" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O100" s="1" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O100" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="P100" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>100</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>69</v>
@@ -6470,19 +6550,19 @@
         <v>53</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G101" s="15" t="s">
-        <v>443</v>
+        <v>337</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>444</v>
+        <v>408</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="1" t="s">
@@ -6494,19 +6574,22 @@
       <c r="N101" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O101" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O101" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="P101" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>69</v>
@@ -6515,19 +6598,19 @@
         <v>53</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G102" s="15" t="s">
-        <v>424</v>
+        <v>337</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>423</v>
+        <v>387</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K102" s="1"/>
       <c r="L102" s="1" t="s">
@@ -6539,19 +6622,22 @@
       <c r="N102" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O102" s="1" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O102" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="P102" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>102</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>69</v>
@@ -6560,19 +6646,19 @@
         <v>53</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G103" s="15" t="s">
-        <v>434</v>
+        <v>337</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K103" s="1"/>
       <c r="L103" s="1" t="s">
@@ -6584,19 +6670,22 @@
       <c r="N103" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O103" s="1" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O103" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="P103" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>69</v>
@@ -6605,22 +6694,22 @@
         <v>53</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G104" s="15" t="s">
-        <v>450</v>
+        <v>337</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>449</v>
+        <v>413</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>451</v>
+        <v>415</v>
       </c>
       <c r="L104" s="1" t="s">
         <v>1</v>
@@ -6631,19 +6720,22 @@
       <c r="N104" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O104" s="1" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O104" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="P104" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>104</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>69</v>
@@ -6652,19 +6744,19 @@
         <v>53</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G105" s="15" t="s">
-        <v>413</v>
+        <v>337</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>414</v>
+        <v>378</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K105" s="1"/>
       <c r="L105" s="1" t="s">
@@ -6676,19 +6768,22 @@
       <c r="N105" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O105" s="1" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O105" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="P105" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>69</v>
@@ -6697,19 +6792,19 @@
         <v>53</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G106" s="15" t="s">
-        <v>426</v>
+        <v>337</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1" t="s">
@@ -6721,19 +6816,22 @@
       <c r="N106" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O106" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O106" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="P106" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>106</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>69</v>
@@ -6742,19 +6840,19 @@
         <v>53</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G107" s="15" t="s">
-        <v>436</v>
+        <v>337</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>435</v>
+        <v>399</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K107" s="1"/>
       <c r="L107" s="1" t="s">
@@ -6766,19 +6864,22 @@
       <c r="N107" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O107" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="108" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O107" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="P107" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>69</v>
@@ -6787,19 +6888,19 @@
         <v>53</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G108" s="15" t="s">
-        <v>427</v>
+        <v>337</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>428</v>
+        <v>392</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K108" s="1"/>
       <c r="L108" s="1" t="s">
@@ -6811,19 +6912,22 @@
       <c r="N108" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O108" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="109" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="O108" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="P108" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>108</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>69</v>
@@ -6832,19 +6936,19 @@
         <v>53</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G109" s="15" t="s">
-        <v>417</v>
+        <v>337</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>381</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>418</v>
+        <v>382</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K109" s="1"/>
       <c r="L109" s="1" t="s">
@@ -6856,19 +6960,22 @@
       <c r="N109" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O109" s="1" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="110" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="O109" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="P109" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>56</v>
@@ -6877,19 +6984,19 @@
         <v>53</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>399</v>
+        <v>337</v>
+      </c>
+      <c r="G110" s="16" t="s">
+        <v>370</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>384</v>
+        <v>478</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K110" s="1"/>
       <c r="L110" s="1" t="s">
@@ -6901,19 +7008,22 @@
       <c r="N110" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O110" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="111" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="O110" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="P110" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>110</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>69</v>
@@ -6922,13 +7032,13 @@
         <v>53</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K111" s="1"/>
       <c r="L111" s="1" t="s">
@@ -6944,15 +7054,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>71</v>
@@ -6961,22 +7071,22 @@
         <v>53</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>385</v>
+        <v>479</v>
+      </c>
+      <c r="I112" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="K112" s="1" t="s">
-        <v>479</v>
+        <v>336</v>
+      </c>
+      <c r="K112" s="7" t="s">
+        <v>452</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>1</v>
@@ -6987,43 +7097,46 @@
       <c r="N112" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O112" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="113" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="O112" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="P112" s="7" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>112</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="L113" s="1" t="s">
         <v>1</v>
@@ -7035,42 +7148,45 @@
         <v>2</v>
       </c>
       <c r="O113" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="114" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+      <c r="P113" s="7" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>1</v>
@@ -7082,42 +7198,45 @@
         <v>2</v>
       </c>
       <c r="O114" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="115" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+      <c r="P114" s="7" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>114</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>1</v>
@@ -7129,10 +7248,13 @@
         <v>2</v>
       </c>
       <c r="O115" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="116" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+        <v>490</v>
+      </c>
+      <c r="P115" s="7" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -7140,19 +7262,19 @@
         <v>48</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K116" s="1"/>
       <c r="L116" s="1" t="s">
@@ -7168,7 +7290,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -7176,19 +7298,19 @@
         <v>49</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K117" s="1"/>
       <c r="L117" s="1" t="s">
@@ -7204,7 +7326,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -7212,19 +7334,19 @@
         <v>50</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K118" s="1"/>
       <c r="L118" s="1" t="s">
@@ -7240,7 +7362,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -7248,19 +7370,19 @@
         <v>51</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K119" s="1"/>
       <c r="L119" s="1" t="s">
@@ -7276,7 +7398,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -7284,19 +7406,19 @@
         <v>52</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K120" s="1"/>
       <c r="L120" s="1" t="s">
@@ -7312,27 +7434,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>120</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K121" s="1"/>
       <c r="L121" s="1" t="s">
@@ -7348,27 +7470,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>53</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>20</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="K122" s="1"/>
       <c r="L122" s="1" t="s">
@@ -7384,7 +7506,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C123" s="1"/>
     </row>
   </sheetData>
